--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5522-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5522-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{646418D3-6D21-46D4-8262-13A44C809A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE408301-DC51-4A2A-9E05-466CFC0801FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{0A072694-4087-4310-9D7C-CA60D122ADFA}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{5FC6C968-ED01-492D-A221-688F1BE0AF97}"/>
   </bookViews>
   <sheets>
     <sheet name="5522-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1583,30 +1583,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FF1E100-7B7D-4AAE-911F-938F2515919C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B3301FA-5BC0-478A-B2D5-C65F885904EB}">
   <dimension ref="A1:X49"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1640,7 +1640,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1676,7 +1676,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1796,7 +1796,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="41">
         <v>2024</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>5.79</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2023</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>6.38</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="41">
         <v>2022</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>9.4499999999999993</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>5.46</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2021</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>8.9600000000000009</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="41">
         <v>2020</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>29</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>7.13</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2019</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>29</v>
       </c>
@@ -3262,7 +3262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="41">
         <v>2018</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>8.85</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2017</v>
       </c>
@@ -3406,7 +3406,7 @@
         <v>8.26</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="41">
         <v>2016</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>2015</v>
       </c>
@@ -3550,7 +3550,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="41">
         <v>2014</v>
       </c>
@@ -3622,7 +3622,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>2013</v>
       </c>
@@ -3694,7 +3694,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="41">
         <v>2012</v>
       </c>
@@ -3766,7 +3766,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>2011</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="41">
         <v>2010</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>2009</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="41">
         <v>2008</v>
       </c>
@@ -4054,7 +4054,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>2007</v>
       </c>
@@ -4126,7 +4126,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="41">
         <v>2006</v>
       </c>
@@ -4198,7 +4198,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="39">
         <v>2005</v>
       </c>
@@ -4270,7 +4270,7 @@
         <v>5.52</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="41">
         <v>2004</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="39">
         <v>2003</v>
       </c>
@@ -4414,7 +4414,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="41">
         <v>2002</v>
       </c>
@@ -4486,7 +4486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="39">
         <v>2001</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="41">
         <v>2000</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="39">
         <v>1999</v>
       </c>
@@ -4702,7 +4702,7 @@
         <v>8.7200000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="43">
         <v>1998</v>
       </c>
@@ -4774,7 +4774,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="45"/>
       <c r="B46" s="46"/>
       <c r="C46" s="22" t="s">
@@ -4802,7 +4802,7 @@
       <c r="W46" s="52"/>
       <c r="X46" s="48"/>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="39">
         <v>1997</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="41">
         <v>1996</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="39" t="s">
         <v>68</v>
       </c>
